--- a/137558_Cuenca_Chancay_-_Huaral/_raw_reportes_xlsx/IDConfig_63327_completo.xlsx
+++ b/137558_Cuenca_Chancay_-_Huaral/_raw_reportes_xlsx/IDConfig_63327_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4b299a18b36c4790"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R6c56933763c64d37"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2025,6 +2025,246 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>05/01/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/01/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/01/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/01/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/01/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/12/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/12/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/12/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/12/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/12/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/12/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/12/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/12/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/12/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/12/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/12/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>20/12/2025</x:t>
         </x:is>
       </x:c>
@@ -5649,178 +5889,1858 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>      5.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/04/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/04/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/04/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/04/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/04/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.5400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/04/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/04/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/04/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/04/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/04/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.5400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/04/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/04/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/04/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/04/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/04/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/04/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/04/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/04/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.3200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/04/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.2400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/04/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.0900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.9500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.6500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.7200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.8500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.8600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.3700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.1500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.6500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.0600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.1700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.8400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.3300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.0900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/03/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.0700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.0300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.2700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.7500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.9300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.7600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.2100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.8300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.9700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.5700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.8300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.0600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.3400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.6200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.1100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.8300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.5100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.1500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>      5.5500</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>20/04/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.6400</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/04/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.8100</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/04/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.6500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/04/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.0000</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/04/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.9500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/04/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.2200</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/04/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.8200</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/04/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.8200</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/04/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.8500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/04/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.3000</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/04/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.8700</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/04/2025</x:t>
+          <x:t>09/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.8200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.0500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.1800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.6100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.7400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.1700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.2400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.8500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/12/2024</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -5835,997 +7755,247 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>08/04/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      7.9100</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/04/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      9.0400</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/04/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     10.2800</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/04/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     11.7300</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/04/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     13.8200</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/04/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     15.3200</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/04/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     15.2400</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/04/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     12.0900</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      9.6600</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      8.3300</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      7.2300</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.6200</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.4700</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.4700</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.9500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      7.6500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      8.4900</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      9.7200</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     10.8500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     11.8600</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     13.3500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     12.3700</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     13.1500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     14.3800</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     11.6500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      8.9300</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      8.1800</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      7.4000</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      7.4800</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      8.5000</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      8.8800</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     10.0600</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     11.1700</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     12.4800</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     10.8400</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     11.3300</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     11.0900</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     11.2300</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/03/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     10.3000</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     10.0700</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     11.0300</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     12.2700</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     12.7500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     11.4800</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     11.9300</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     10.2300</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      9.8800</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      8.9900</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      7.7600</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      8.2200</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      8.3000</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      9.2100</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     10.8300</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     12.4100</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     12.9700</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     12.5700</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      9.4900</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      8.5100</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      9.0000</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     10.8300</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     11.0600</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     11.3400</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     11.6200</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      8.2200</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.8000</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.9900</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/02/2025</x:t>
+          <x:t>17/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.3100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.1600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.9300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.7700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.5300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.0500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.5100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.8500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/12/2024</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -6840,187 +8010,37 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>31/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.9200</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.1100</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.6500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.8500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.1100</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.2500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.3100</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.8200</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.4300</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.8100</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.4800</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.8300</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/01/2025</x:t>
+          <x:t>30/11/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/11/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.7600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/11/2024</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -7035,786 +8055,6 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>18/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.4200</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.3200</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.5100</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.8000</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.4800</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.9600</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.1500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.5500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.0100</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      7.4100</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      8.8200</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     10.0500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     12.1800</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     13.6100</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     13.7400</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     11.1700</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      8.2200</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.6800</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.2400</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0600</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.3300</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.6600</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.9800</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.8500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.1900</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.8300</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.7900</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.6000</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.9900</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.6600</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      7.4400</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      9.3100</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      8.0400</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      7.4300</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.1600</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.9300</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.7700</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.3300</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.5300</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.1600</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.2900</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.6800</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.0500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.5100</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      7.3400</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      8.8500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      8.1100</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.4800</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/11/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.6200</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/11/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.7600</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/11/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      4.1500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>27/11/2024</x:t>
         </x:is>
       </x:c>
@@ -7824,7 +8064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.6000</x:v>
+        <x:v>      2.5900</x:v>
       </x:c>
     </x:row>
     <x:row>
